--- a/data/TeledyneDatabase.xlsx
+++ b/data/TeledyneDatabase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwprod-my.sharepoint.com/personal/ssridhara_wisc_edu/Documents/Spring 2023/DiffCat_METALS/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="11_80DF9403C6C9AE305A670F3DBE162FB94980909A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48A727DB-D4E7-4512-B9E0-1EDC875295C4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134C8861-EB35-4A47-9005-5BCF681FCA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
@@ -281,14 +281,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -326,7 +322,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -432,7 +428,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -574,7 +570,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -583,23 +579,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" customWidth="1"/>
-    <col min="2" max="2" width="5.81640625" customWidth="1"/>
-    <col min="3" max="3" width="8.453125" customWidth="1"/>
-    <col min="4" max="4" width="24.1796875" customWidth="1"/>
-    <col min="5" max="5" width="18.26953125" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" customWidth="1"/>
-    <col min="8" max="8" width="24.81640625" customWidth="1"/>
-    <col min="9" max="9" width="25.6328125" customWidth="1"/>
-    <col min="10" max="10" width="21.36328125" customWidth="1"/>
-    <col min="11" max="11" width="21.453125" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.3828125" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" customWidth="1"/>
+    <col min="3" max="3" width="8.4609375" customWidth="1"/>
+    <col min="4" max="4" width="24.15234375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="18.23046875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.15234375" customWidth="1"/>
+    <col min="7" max="7" width="10.921875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="24.84375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="25.61328125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="21.3828125" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="21.4609375" customWidth="1"/>
+    <col min="12" max="12" width="13.84375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -637,7 +633,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -675,7 +671,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
@@ -713,7 +709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -751,7 +747,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
@@ -789,7 +785,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
@@ -827,7 +823,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
@@ -865,7 +861,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
@@ -903,7 +899,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -941,7 +937,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>19</v>
       </c>
@@ -979,7 +975,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
@@ -1017,7 +1013,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
@@ -1055,7 +1051,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1093,7 +1089,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>24</v>
       </c>
@@ -1131,7 +1127,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
@@ -1169,7 +1165,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>26</v>
       </c>
@@ -1207,7 +1203,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
@@ -1245,7 +1241,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
         <v>29</v>
       </c>
@@ -1283,7 +1279,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>32</v>
       </c>
@@ -1321,7 +1317,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>33</v>
       </c>
@@ -1359,7 +1355,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>34</v>
       </c>
